--- a/Hershey DCF-LBO.xlsx
+++ b/Hershey DCF-LBO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sol/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0A607F-02D3-A441-A9EC-C0AC8B06016E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421C4AB0-AAEF-2447-A621-146AABB736E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover &amp; Instructions" sheetId="1" r:id="rId1"/>
@@ -771,7 +771,7 @@
     <author>tc={9FF3C24B-97B3-1B42-9356-040288047E6C}</author>
   </authors>
   <commentList>
-    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -784,7 +784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
       <text>
         <r>
           <rPr>
@@ -797,7 +797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="1" shapeId="0" xr:uid="{A0A92BBB-1C77-1649-B9D4-5E0DE7F20F10}">
+    <comment ref="D11" authorId="1" shapeId="0" xr:uid="{A0A92BBB-1C77-1649-B9D4-5E0DE7F20F10}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -805,7 +805,7 @@
     Mega Cap Assumption Rate</t>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
+    <comment ref="C19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
       <text>
         <r>
           <rPr>
@@ -818,7 +818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
+    <comment ref="C25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
       <text>
         <r>
           <rPr>
@@ -831,7 +831,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="2" shapeId="0" xr:uid="{9FF3C24B-97B3-1B42-9356-040288047E6C}">
+    <comment ref="D25" authorId="2" shapeId="0" xr:uid="{9FF3C24B-97B3-1B42-9356-040288047E6C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -839,7 +839,7 @@
     5% base with 5% credit swings and .25% fees</t>
       </text>
     </comment>
-    <comment ref="C28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
+    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
       <text>
         <r>
           <rPr>
@@ -852,7 +852,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
+    <comment ref="C30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
       <text>
         <r>
           <rPr>
@@ -865,7 +865,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
+    <comment ref="D33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
       <text>
         <r>
           <rPr>
@@ -878,11 +878,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
+    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
@@ -890,7 +891,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000009000000}">
+    <comment ref="F33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000009000000}">
       <text>
         <r>
           <rPr>
@@ -902,7 +903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000A000000}">
+    <comment ref="G33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -914,7 +915,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000B000000}">
+    <comment ref="H33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -926,7 +927,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000C000000}">
+    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -944,7 +945,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="266">
   <si>
     <t>The Hershey Company (NYSE: HSY)</t>
   </si>
@@ -1739,6 +1740,9 @@
   </si>
   <si>
     <t>n/a</t>
+  </si>
+  <si>
+    <t>Normalized EBITDA (FY2024A)</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1759,7 @@
     <numFmt numFmtId="170" formatCode="0.000"/>
     <numFmt numFmtId="171" formatCode="0.00%;\(0.00%\);\-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1819,12 +1823,6 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1898,9 +1896,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1943,6 +1938,9 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2249,10 +2247,10 @@
 
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D10" dT="2026-09-20T21:08:13.65" personId="{4387A116-ADE4-C040-9C02-5541A53D000C}" id="{A0A92BBB-1C77-1649-B9D4-5E0DE7F20F10}">
+  <threadedComment ref="D11" dT="2026-09-20T21:08:13.65" personId="{4387A116-ADE4-C040-9C02-5541A53D000C}" id="{A0A92BBB-1C77-1649-B9D4-5E0DE7F20F10}">
     <text>Mega Cap Assumption Rate</text>
   </threadedComment>
-  <threadedComment ref="D24" dT="2026-09-20T22:07:36.27" personId="{4387A116-ADE4-C040-9C02-5541A53D000C}" id="{9FF3C24B-97B3-1B42-9356-040288047E6C}">
+  <threadedComment ref="D25" dT="2026-09-20T22:07:36.27" personId="{4387A116-ADE4-C040-9C02-5541A53D000C}" id="{9FF3C24B-97B3-1B42-9356-040288047E6C}">
     <text>5% base with 5% credit swings and .25% fees</text>
   </threadedComment>
 </ThreadedComments>
@@ -2337,7 +2335,7 @@
       <c r="B13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2345,7 +2343,7 @@
       <c r="B14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2353,7 +2351,7 @@
       <c r="B15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2361,7 +2359,7 @@
       <c r="B16" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2369,7 +2367,7 @@
       <c r="B17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2377,7 +2375,7 @@
       <c r="B18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2391,7 +2389,7 @@
       <c r="B21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2399,7 +2397,7 @@
       <c r="B22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2407,7 +2405,7 @@
       <c r="B23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2415,7 +2413,7 @@
       <c r="B24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2429,7 +2427,7 @@
       <c r="B27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2437,7 +2435,7 @@
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2445,7 +2443,7 @@
       <c r="B31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2459,7 +2457,7 @@
       <c r="B35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2467,7 +2465,7 @@
       <c r="B36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2475,7 +2473,7 @@
       <c r="B37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2483,7 +2481,7 @@
       <c r="B38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2491,7 +2489,7 @@
       <c r="B39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2499,7 +2497,7 @@
       <c r="B40" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2507,7 +2505,7 @@
       <c r="B42" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2549,7 +2547,7 @@
       <c r="B6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>169.79</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -2560,7 +2558,7 @@
       <c r="B7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>200.93</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -2571,7 +2569,7 @@
       <c r="B8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>203.4</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -2582,7 +2580,7 @@
       <c r="B9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <f>C6*C7</f>
         <v>34115.904699999999</v>
       </c>
@@ -2591,7 +2589,7 @@
       <c r="B10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>5.81</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -2608,7 +2606,7 @@
       <c r="B13" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f>'Balance Sheet'!E20+'Balance Sheet'!E23</f>
         <v>4830.55</v>
       </c>
@@ -2617,7 +2615,7 @@
       <c r="B14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f>'Balance Sheet'!E7</f>
         <v>925.86</v>
       </c>
@@ -2626,7 +2624,7 @@
       <c r="B15" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <f>C13-C14</f>
         <v>3904.69</v>
       </c>
@@ -2635,7 +2633,7 @@
       <c r="B16" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="12">
         <f>C9+C15</f>
         <v>38020.594700000001</v>
       </c>
@@ -2650,7 +2648,7 @@
       <c r="B19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="13">
         <v>0.05</v>
       </c>
       <c r="E19" s="5" t="s">
@@ -2661,10 +2659,10 @@
       <c r="B20" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
         <v>0.45</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="1" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2672,7 +2670,7 @@
       <c r="B21" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="15">
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
@@ -2680,7 +2678,7 @@
       <c r="B22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="15">
         <f>C19+(C21*C20)</f>
         <v>6.9125000000000006E-2</v>
       </c>
@@ -2689,7 +2687,7 @@
       <c r="B23" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="15">
         <f>'Income Statement'!F14/'Balance Sheet'!E37</f>
         <v>3.9374398360435145E-2</v>
       </c>
@@ -2698,7 +2696,7 @@
       <c r="B24" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="15">
         <v>0.16500000000000001</v>
       </c>
     </row>
@@ -2706,7 +2704,7 @@
       <c r="B25" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="15">
         <f>C23*(1-C24)</f>
         <v>3.2877622630963346E-2</v>
       </c>
@@ -2715,7 +2713,7 @@
       <c r="B26" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="15">
         <f>(C9)/(C9+C13)</f>
         <v>0.87596945505799784</v>
       </c>
@@ -2724,17 +2722,17 @@
       <c r="B27" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="15">
         <f>C13/(C9+C13)</f>
         <v>0.12403054494200212</v>
       </c>
-      <c r="E27" s="45"/>
+      <c r="E27" s="44"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="16">
         <f>(C27*C25)+(C26*C22)</f>
         <v>6.4629218032199981E-2</v>
       </c>
@@ -2768,17 +2766,17 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="18"/>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2786,16 +2784,16 @@
       <c r="B6" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <v>10419.294</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>11164.992</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <v>11202.3</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <v>11692.6</v>
       </c>
     </row>
@@ -2803,16 +2801,16 @@
       <c r="B7" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>5920.509</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>6167.1760000000004</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <v>5901.4</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <v>7769.9</v>
       </c>
     </row>
@@ -2820,19 +2818,19 @@
       <c r="B8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <f>C6-C7</f>
         <v>4498.7849999999999</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <f>D6-D7</f>
         <v>4997.8159999999998</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <f>E6-E7</f>
         <v>5300.9</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f>F6-F7</f>
         <v>3922.7000000000007</v>
       </c>
@@ -2841,19 +2839,19 @@
       <c r="B9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="15">
         <f>C8/C6</f>
         <v>0.43177445611957971</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <f t="shared" ref="D9:F9" si="0">D8/D6</f>
         <v>0.44763274348965049</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="15">
         <f t="shared" si="0"/>
         <v>0.4731974683770297</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <f t="shared" si="0"/>
         <v>0.33548569180507337</v>
       </c>
@@ -2862,16 +2860,16 @@
       <c r="B10" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>2236.009</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>2436.5079999999998</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="19">
         <v>2373.6</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="19">
         <v>2460.6</v>
       </c>
     </row>
@@ -2879,16 +2877,16 @@
       <c r="B11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <v>1.9890000000000001</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>0.441</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="19">
         <v>29.1</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="19">
         <v>20.6</v>
       </c>
     </row>
@@ -2896,19 +2894,19 @@
       <c r="B12" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <f>C8-C10-C11</f>
         <v>2260.7869999999998</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f>D8-D10-D11</f>
         <v>2560.8670000000002</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <f>E8-E10-E11</f>
         <v>2898.2</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <f>F8-F10-F11</f>
         <v>1441.5000000000009</v>
       </c>
@@ -2917,19 +2915,19 @@
       <c r="B13" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="15">
         <f>C12/C6</f>
         <v>0.21698082422858975</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <f t="shared" ref="D13:F13" si="1">D12/D6</f>
         <v>0.22936577115326193</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <f t="shared" si="1"/>
         <v>0.25871472822545372</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <f t="shared" si="1"/>
         <v>0.12328310213297307</v>
       </c>
@@ -2938,16 +2936,16 @@
       <c r="B14" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="19">
         <v>137.55699999999999</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="19">
         <v>151.785</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="19">
         <v>165.7</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="19">
         <v>190.2</v>
       </c>
     </row>
@@ -2955,16 +2953,16 @@
       <c r="B15" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="19">
         <v>206.15899999999999</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="19">
         <v>237.21799999999999</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="19">
         <v>258.60000000000002</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="19">
         <v>37.1</v>
       </c>
     </row>
@@ -2972,19 +2970,19 @@
       <c r="B16" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <f>C12-C14-C15</f>
         <v>1917.0709999999999</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <f>D12-D14-D15</f>
         <v>2171.8640000000005</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <f>E12-E14-E15</f>
         <v>2473.9</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <f>F12-F14-F15</f>
         <v>1214.200000000001</v>
       </c>
@@ -2993,16 +2991,16 @@
       <c r="B17" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="19">
         <v>272.25400000000002</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="19">
         <v>310.077</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="19">
         <v>252.7</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="19">
         <v>330.9</v>
       </c>
     </row>
@@ -3010,19 +3008,19 @@
       <c r="B18" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="15">
         <f>C17/C16</f>
         <v>0.14201560609909597</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <f t="shared" ref="D18:F18" si="2">D17/D16</f>
         <v>0.14276998928109677</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="15">
         <f t="shared" si="2"/>
         <v>0.10214640850479</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <f t="shared" si="2"/>
         <v>0.27252511942019414</v>
       </c>
@@ -3031,41 +3029,41 @@
       <c r="B19" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="20">
         <f>C16-C17</f>
         <v>1644.817</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="20">
         <f>D16-D17</f>
         <v>1861.7870000000005</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <f>E16-E17</f>
         <v>2221.2000000000003</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="20">
         <f>F16-F17</f>
         <v>883.30000000000098</v>
       </c>
-      <c r="H19" s="41"/>
+      <c r="H19" s="40"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="15">
         <f>C19/C6</f>
         <v>0.15786261525972872</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <f t="shared" ref="D20:F20" si="3">D19/D6</f>
         <v>0.16675220188245549</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="15">
         <f t="shared" si="3"/>
         <v>0.19828071021129592</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <f t="shared" si="3"/>
         <v>7.5543506149188464E-2</v>
       </c>
@@ -3074,16 +3072,16 @@
       <c r="B22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <v>7.96</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>9.06</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <v>10.92</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="8">
         <v>4.34</v>
       </c>
     </row>
@@ -3091,16 +3089,16 @@
       <c r="B23" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>206.57499999999999</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>205.547</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>203.5</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="9">
         <v>203.4</v>
       </c>
     </row>
@@ -3117,19 +3115,19 @@
       <c r="B26" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="21">
         <f>'Cash Flow Statement'!C8</f>
         <v>379</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <f>'Cash Flow Statement'!D8</f>
         <v>420</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="21">
         <f>'Cash Flow Statement'!E8</f>
         <v>455</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="21">
         <f>'Cash Flow Statement'!F8</f>
         <v>504</v>
       </c>
@@ -3138,70 +3136,70 @@
       <c r="B27" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <f>C12+C26</f>
         <v>2639.7869999999998</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <f>D12+D26</f>
         <v>2980.8670000000002</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="10">
         <f>E12+E26</f>
         <v>3353.2</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="10">
         <f>F12+F26</f>
         <v>1945.5000000000009</v>
       </c>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="41"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="40"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="15">
         <f>C27/C6</f>
         <v>0.25335564962462909</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="15">
         <f t="shared" ref="D28:F28" si="4">D27/D6</f>
         <v>0.26698335296612841</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="15">
         <f t="shared" si="4"/>
         <v>0.29933138730439285</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="15">
         <f t="shared" si="4"/>
         <v>0.16638728768622896</v>
       </c>
-      <c r="I28" s="41"/>
+      <c r="I28" s="40"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="15">
         <f>(D6/C6)-1</f>
         <v>7.1568956591492761E-2</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="15">
         <f t="shared" ref="E29:F29" si="5">(E6/D6)-1</f>
         <v>3.3415160530343435E-3</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="15">
         <f t="shared" si="5"/>
         <v>4.3767797684404197E-2</v>
       </c>
-      <c r="J29" s="41"/>
+      <c r="J29" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3232,14 +3230,14 @@
       </c>
     </row>
     <row r="5" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="18"/>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3255,13 +3253,13 @@
       <c r="B7" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>401.9</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>730.75</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <v>925.86</v>
       </c>
     </row>
@@ -3269,13 +3267,13 @@
       <c r="B8" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="19">
         <v>823.62</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>800.4</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <v>729.55</v>
       </c>
     </row>
@@ -3283,13 +3281,13 @@
       <c r="B9" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>1341</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>1254</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="19">
         <v>1429</v>
       </c>
     </row>
@@ -3297,13 +3295,13 @@
       <c r="B10" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>345.59</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>974.21</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="19">
         <v>504.24</v>
       </c>
     </row>
@@ -3311,15 +3309,15 @@
       <c r="B11" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <f>SUM(C7:C10)</f>
         <v>2912.11</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f>SUM(D7:D10)</f>
         <v>3759.36</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <f>SUM(E7:E10)</f>
         <v>3588.6499999999996</v>
       </c>
@@ -3328,13 +3326,13 @@
       <c r="B12" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="19">
         <v>3618</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="19">
         <v>3797</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="19">
         <v>3855</v>
       </c>
     </row>
@@ -3342,13 +3340,13 @@
       <c r="B13" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="19">
         <v>2696</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="19">
         <v>2706</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="19">
         <v>2996</v>
       </c>
     </row>
@@ -3356,13 +3354,13 @@
       <c r="B14" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="19">
         <v>2239</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="19">
         <v>2241</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="19">
         <v>2827</v>
       </c>
     </row>
@@ -3370,13 +3368,13 @@
       <c r="B15" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="19">
         <v>438</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="19">
         <v>444</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="19">
         <v>474</v>
       </c>
     </row>
@@ -3384,15 +3382,15 @@
       <c r="B16" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <f>C11+C12+C13+C14+C15</f>
         <v>11903.11</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <f>D11+D12+D13+D14+D15</f>
         <v>12947.36</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <f>E11+E12+E13+E14+E15</f>
         <v>13740.65</v>
       </c>
@@ -3409,13 +3407,13 @@
       <c r="B19" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="19">
         <v>1086</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="19">
         <v>1159</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="19">
         <v>1256</v>
       </c>
     </row>
@@ -3423,13 +3421,13 @@
       <c r="B20" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="19">
         <v>719.84</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="19">
         <v>1307</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="19">
         <v>218.55</v>
       </c>
     </row>
@@ -3437,13 +3435,13 @@
       <c r="B21" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="19">
         <v>1202.1600000000001</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="19">
         <v>1463</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="19">
         <v>1539.45</v>
       </c>
     </row>
@@ -3451,15 +3449,15 @@
       <c r="B22" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <f>SUM(C19:C21)</f>
         <v>3008</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <f>SUM(D19:D21)</f>
         <v>3929</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="10">
         <f>SUM(E19:E21)</f>
         <v>3014</v>
       </c>
@@ -3468,13 +3466,13 @@
       <c r="B23" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="19">
         <v>3719</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="19">
         <v>3122</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="19">
         <v>4612</v>
       </c>
     </row>
@@ -3482,13 +3480,13 @@
       <c r="B24" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="19">
         <v>345.7</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="19">
         <v>424.24</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="19">
         <v>679.54</v>
       </c>
     </row>
@@ -3496,13 +3494,13 @@
       <c r="B25" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="19">
         <v>732.3</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="19">
         <v>756.47</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="19">
         <v>789.84</v>
       </c>
     </row>
@@ -3510,15 +3508,15 @@
       <c r="B26" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <f>C22+C23+C24+C25</f>
         <v>7805</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <f>D22+D23+D24+D25</f>
         <v>8231.7099999999991</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="10">
         <f>E22+E23+E24+E25</f>
         <v>9095.380000000001</v>
       </c>
@@ -3535,13 +3533,13 @@
       <c r="B29" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="22">
         <v>4099</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="22">
         <v>4715</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="22">
         <v>4637</v>
       </c>
     </row>
@@ -3549,15 +3547,15 @@
       <c r="B30" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="20">
         <f>C26+C29</f>
         <v>11904</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="20">
         <f>D26+D29</f>
         <v>12946.71</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="20">
         <f>E26+E29</f>
         <v>13732.380000000001</v>
       </c>
@@ -3566,19 +3564,19 @@
       <c r="B32" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="23">
         <f>C16-C30</f>
         <v>-0.88999999999941792</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="23">
         <f>D16-D30</f>
         <v>0.65000000000145519</v>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="23">
         <f>E16-E30</f>
         <v>8.2699999999986176</v>
       </c>
-      <c r="F32" s="40" t="s">
+      <c r="F32" s="39" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3594,15 +3592,15 @@
       <c r="B36" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="24">
         <f>C11/C22</f>
         <v>0.96812167553191497</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="24">
         <f t="shared" ref="D36:E36" si="0">D11/D22</f>
         <v>0.95682361924153736</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="24">
         <f t="shared" si="0"/>
         <v>1.1906602521566023</v>
       </c>
@@ -3611,15 +3609,15 @@
       <c r="B37" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="21">
         <f>C20+C23</f>
         <v>4438.84</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="21">
         <f>D20+D23</f>
         <v>4429</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E37" s="21">
         <f>E20+E23</f>
         <v>4830.55</v>
       </c>
@@ -3628,15 +3626,15 @@
       <c r="B38" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="25">
         <f>(C37-C11)/'Income Statement'!C27</f>
         <v>0.57835348079220028</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="25">
         <f>(D37-D11)/'Income Statement'!D27</f>
         <v>0.22464605096436702</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="25">
         <f>(E37-E11)/'Income Statement'!E27</f>
         <v>0.37036263867350611</v>
       </c>
@@ -3645,15 +3643,15 @@
       <c r="B39" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="25">
         <f>C37/C29</f>
         <v>1.0829080263478899</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="25">
         <f t="shared" ref="D39:E39" si="1">D37/D29</f>
         <v>0.93934252386002126</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="25">
         <f t="shared" si="1"/>
         <v>1.0417403493638129</v>
       </c>
@@ -3687,17 +3685,17 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="18"/>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3714,16 +3712,16 @@
       <c r="B7" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>1644.817</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>1861.787</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <v>2221.1999999999998</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <v>883.3</v>
       </c>
     </row>
@@ -3731,16 +3729,16 @@
       <c r="B8" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="19">
         <v>379</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>420</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <v>455</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="19">
         <v>504</v>
       </c>
     </row>
@@ -3748,16 +3746,16 @@
       <c r="B9" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <v>66</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>81</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="19">
         <v>44</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="19">
         <v>65</v>
       </c>
     </row>
@@ -3765,16 +3763,16 @@
       <c r="B10" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>-108</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>-369</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="19">
         <v>-69</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="19">
         <v>40</v>
       </c>
     </row>
@@ -3782,16 +3780,16 @@
       <c r="B11" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>2328</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="26">
         <v>2323</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="26">
         <v>2532</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="26">
         <v>2277</v>
       </c>
     </row>
@@ -3808,16 +3806,16 @@
       <c r="B14" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="19">
         <v>-519</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="19">
         <v>-771</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="19">
         <v>-606</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="19">
         <v>-455</v>
       </c>
     </row>
@@ -3825,16 +3823,16 @@
       <c r="B15" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="19">
         <v>-166</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="19">
         <v>-76</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="19">
         <v>-756</v>
       </c>
     </row>
@@ -3842,16 +3840,16 @@
       <c r="B16" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>-787</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="26">
         <v>-1199</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="26">
         <v>-960</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="26">
         <v>-1279</v>
       </c>
     </row>
@@ -3868,55 +3866,55 @@
       <c r="B19" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="19">
         <v>-775</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="19">
         <v>-889</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="19">
         <v>-1085</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="19">
         <v>-1085</v>
       </c>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B20" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="19">
         <v>-424</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="19">
         <v>-300</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="19">
         <v>-527</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="19">
         <v>-19</v>
       </c>
-      <c r="M20" s="43"/>
+      <c r="M20" s="42"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B21" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="19">
         <v>-250</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="19">
         <v>15</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="19">
         <v>301</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="19">
         <v>279</v>
       </c>
     </row>
@@ -3924,64 +3922,64 @@
       <c r="B22" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="26">
         <v>-1416</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="26">
         <v>-1148</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="26">
         <v>-1297</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="26">
         <v>-803</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="20">
         <f>C11+C16+C22</f>
         <v>125</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="20">
         <f>D11+D16+D22</f>
         <v>-24</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="20">
         <f>E11+E16+E22</f>
         <v>275</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="20">
         <f>F11+F16+F22</f>
         <v>195</v>
       </c>
-      <c r="J24" s="43"/>
+      <c r="J24" s="42"/>
     </row>
     <row r="25" spans="2:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="42"/>
-      <c r="P25" s="42"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="41"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="41"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B27" s="6" t="s">
@@ -3991,26 +3989,26 @@
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="44"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="43"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="10">
         <f>C11+C14</f>
         <v>1809</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <f>D11+D14</f>
         <v>1552</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="10">
         <f>E11+E14</f>
         <v>1926</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="10">
         <f>F11+F14</f>
         <v>1822</v>
       </c>
@@ -4019,19 +4017,19 @@
       <c r="B29" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="15">
         <f>C28/'Income Statement'!C6</f>
         <v>0.17362020881645149</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="15">
         <f>D28/'Income Statement'!D6</f>
         <v>0.13900592136564002</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="15">
         <f>E28/'Income Statement'!E6</f>
         <v>0.17192897887041056</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="15">
         <f>F28/'Income Statement'!F6</f>
         <v>0.15582505174212749</v>
       </c>
@@ -4040,19 +4038,19 @@
       <c r="B30" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="15">
         <f>C28/'Income Statement'!C27</f>
         <v>0.68528256257038922</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="15">
         <f>D28/'Income Statement'!D27</f>
         <v>0.52065389029433384</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="15">
         <f>E28/'Income Statement'!E27</f>
         <v>0.57437671477991181</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="15">
         <f>F28/'Income Statement'!F27</f>
         <v>0.93652017476227145</v>
       </c>
@@ -4090,23 +4088,23 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="18"/>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>165</v>
       </c>
     </row>
@@ -4125,27 +4123,27 @@
       <c r="B7" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>'Income Statement'!F6</f>
         <v>11692.6</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <f>C7*(1+D8)</f>
         <v>12335.692999999999</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <f>D7*(1+E8)</f>
         <v>13014.156114999998</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <f>E7*(1+F8)</f>
         <v>13729.934701324997</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <f>F7*(1+G8)</f>
         <v>14485.081109897872</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <f>G7*(1+H8)</f>
         <v>15281.760570942253</v>
       </c>
@@ -4154,19 +4152,19 @@
       <c r="B8" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>5.5E-2</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <v>5.5E-2</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>5.5E-2</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <v>5.5E-2</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="15">
         <v>5.5E-2</v>
       </c>
     </row>
@@ -4185,19 +4183,19 @@
       <c r="B11" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>0.247</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>0.247</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="15">
         <v>0.247</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <v>0.247</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <v>0.247</v>
       </c>
     </row>
@@ -4205,23 +4203,23 @@
       <c r="B12" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f>D7*D11</f>
         <v>3046.9161709999998</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <f>E7*E11</f>
         <v>3214.4965604049994</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <f>F7*F11</f>
         <v>3391.2938712272744</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <f>G7*G11</f>
         <v>3577.8150341447745</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="10">
         <f>H7*H11</f>
         <v>3774.5948610227365</v>
       </c>
@@ -4230,19 +4228,19 @@
       <c r="B13" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="15">
         <v>3.9E-2</v>
       </c>
     </row>
@@ -4250,23 +4248,23 @@
       <c r="B14" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <f>-D7*D13</f>
         <v>-481.09202699999997</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="21">
         <f>-E7*E13</f>
         <v>-507.5520884849999</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <f>-F7*F13</f>
         <v>-535.46745335167486</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <f>-G7*G13</f>
         <v>-564.91816328601703</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <f>-H7*H13</f>
         <v>-595.98866226674784</v>
       </c>
@@ -4275,23 +4273,23 @@
       <c r="B15" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <f>D12+D14</f>
         <v>2565.8241439999997</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="10">
         <f>E12+E14</f>
         <v>2706.9444719199996</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <f>F12+F14</f>
         <v>2855.8264178755994</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <f>G12+G14</f>
         <v>3012.8968708587572</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="10">
         <f>H12+H14</f>
         <v>3178.6061987559888</v>
       </c>
@@ -4300,23 +4298,23 @@
       <c r="B16" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <f>Assumptions!$C$24</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <f>Assumptions!$C$24</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="27">
         <f>Assumptions!$C$24</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="27">
         <f>Assumptions!$C$24</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="27">
         <f>Assumptions!$C$24</f>
         <v>0.16500000000000001</v>
       </c>
@@ -4325,23 +4323,23 @@
       <c r="B17" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <f>-D15*D16</f>
         <v>-423.36098375999995</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="21">
         <f>-E15*E16</f>
         <v>-446.64583786679998</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="21">
         <f>-F15*F16</f>
         <v>-471.21135894947395</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="21">
         <f>-G15*G16</f>
         <v>-497.12798369169496</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="21">
         <f>-H15*H16</f>
         <v>-524.47002279473816</v>
       </c>
@@ -4350,23 +4348,23 @@
       <c r="B18" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <f>D15+D17</f>
         <v>2142.4631602399995</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="10">
         <f>E15+E17</f>
         <v>2260.2986340531997</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <f>F15+F17</f>
         <v>2384.6150589261256</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="10">
         <f>G15+G17</f>
         <v>2515.7688871670621</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="10">
         <f>H15+H17</f>
         <v>2654.1361759612505</v>
       </c>
@@ -4386,23 +4384,23 @@
       <c r="B21" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <f>-D14</f>
         <v>481.09202699999997</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="21">
         <f>-E14</f>
         <v>507.5520884849999</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="21">
         <f>-F14</f>
         <v>535.46745335167486</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="21">
         <f>-G14</f>
         <v>564.91816328601703</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="21">
         <f>-H14</f>
         <v>595.98866226674784</v>
       </c>
@@ -4411,19 +4409,19 @@
       <c r="B22" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="15">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="15">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="15">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="15">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="15">
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
@@ -4431,23 +4429,23 @@
       <c r="B23" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <f>-D7*D22</f>
         <v>-653.79172899999992</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="21">
         <f>-E7*E22</f>
         <v>-689.7502740949999</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="21">
         <f>-F7*F22</f>
         <v>-727.68653917022482</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="21">
         <f>-G7*G22</f>
         <v>-767.70929882458722</v>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="21">
         <f>-H7*H22</f>
         <v>-809.93331025993939</v>
       </c>
@@ -4456,19 +4454,19 @@
       <c r="B24" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="15">
         <v>1.15E-2</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="15">
         <v>1.15E-2</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="15">
         <v>1.15E-2</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="15">
         <v>1.15E-2</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="15">
         <v>1.15E-2</v>
       </c>
     </row>
@@ -4476,23 +4474,23 @@
       <c r="B25" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <f>-D7*D24</f>
         <v>-141.86046949999999</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="21">
         <f>-E7*E24</f>
         <v>-149.66279532249996</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="21">
         <f>-F7*F24</f>
         <v>-157.89424906523746</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="21">
         <f>-G7*G24</f>
         <v>-166.57843276382553</v>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="21">
         <f>-H7*H24</f>
         <v>-175.74024656583592</v>
       </c>
@@ -4501,23 +4499,23 @@
       <c r="B26" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="20">
         <f>D18+D21+D23+D25</f>
         <v>1827.9029887399997</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="20">
         <f>E18+E21+E23+E25</f>
         <v>1928.4376531206997</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="20">
         <f>F18+F21+F23+F25</f>
         <v>2034.5017240423381</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="20">
         <f>G18+G21+G23+G25</f>
         <v>2146.3993188646659</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="20">
         <f>H18+H21+H23+H25</f>
         <v>2264.4512814022228</v>
       </c>
@@ -4537,23 +4535,23 @@
       <c r="B29" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="27">
         <f>Assumptions!$C$28</f>
         <v>6.4629218032199981E-2</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="27">
         <f>Assumptions!$C$28</f>
         <v>6.4629218032199981E-2</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="27">
         <f>Assumptions!$C$28</f>
         <v>6.4629218032199981E-2</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="27">
         <f>Assumptions!$C$28</f>
         <v>6.4629218032199981E-2</v>
       </c>
-      <c r="H29" s="28">
+      <c r="H29" s="27">
         <f>Assumptions!$C$28</f>
         <v>6.4629218032199981E-2</v>
       </c>
@@ -4562,19 +4560,19 @@
       <c r="B30" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="28">
         <v>1</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="28">
         <v>2</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="28">
         <v>3</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="28">
         <v>4</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="28">
         <v>5</v>
       </c>
     </row>
@@ -4582,23 +4580,23 @@
       <c r="B31" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="29">
         <f>1/(1+D29)^D30</f>
         <v>0.93929415336575406</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="29">
         <f>1/(1+E29)^E30</f>
         <v>0.8822735065470888</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="29">
         <f>1/(1+F29)^F30</f>
         <v>0.82871434636918284</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="29">
         <f>1/(1+G29)^G30</f>
         <v>0.77840654035489587</v>
       </c>
-      <c r="H31" s="30">
+      <c r="H31" s="29">
         <f>1/(1+H29)^H30</f>
         <v>0.73115271229701762</v>
       </c>
@@ -4607,23 +4605,23 @@
       <c r="B32" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <f>D26*D31</f>
         <v>1716.9385902432696</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="10">
         <f>E26*E31</f>
         <v>1701.4094503762383</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="10">
         <f>F26*F31</f>
         <v>1686.0207664267218</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="10">
         <f>G26*G31</f>
         <v>1670.7712680175496</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="10">
         <f>H26*H31</f>
         <v>1655.6596962616923</v>
       </c>
@@ -4643,7 +4641,7 @@
       <c r="B35" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -4651,7 +4649,7 @@
       <c r="B36" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36" s="21">
         <f>IFERROR(H26*(1+$E$35)/(Assumptions!$C$28-$E$35),0)</f>
         <v>58569.476731823022</v>
       </c>
@@ -4660,7 +4658,7 @@
       <c r="B37" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="10">
         <f>H36*H31</f>
         <v>42823.231770289465</v>
       </c>
@@ -4669,7 +4667,7 @@
       <c r="B39" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="25">
         <v>15</v>
       </c>
     </row>
@@ -4677,7 +4675,7 @@
       <c r="B40" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="H40" s="22">
+      <c r="H40" s="21">
         <f>H12*$E$39</f>
         <v>56618.922915341049</v>
       </c>
@@ -4686,7 +4684,7 @@
       <c r="B41" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="10">
         <f>H40*H31</f>
         <v>41397.079056887371</v>
       </c>
@@ -4706,7 +4704,7 @@
       <c r="B44" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="21">
         <f>SUM(D32:H32)</f>
         <v>8430.7997713254699</v>
       </c>
@@ -4715,7 +4713,7 @@
       <c r="B45" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <f>C44+H37</f>
         <v>51254.031541614939</v>
       </c>
@@ -4724,7 +4722,7 @@
       <c r="B46" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C46" s="13">
+      <c r="C46" s="12">
         <f>C44+H41</f>
         <v>49827.878828212837</v>
       </c>
@@ -4733,7 +4731,7 @@
       <c r="B47" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="11">
         <f>-Assumptions!$C$15</f>
         <v>-3904.69</v>
       </c>
@@ -4742,7 +4740,7 @@
       <c r="B48" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="10">
         <f>C45+C47</f>
         <v>47349.341541614936</v>
       </c>
@@ -4751,7 +4749,7 @@
       <c r="B49" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="13">
+      <c r="C49" s="12">
         <f>C46+C47</f>
         <v>45923.188828212835</v>
       </c>
@@ -4760,7 +4758,7 @@
       <c r="B50" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="30">
         <f>Assumptions!$C$8</f>
         <v>203.4</v>
       </c>
@@ -4769,7 +4767,7 @@
       <c r="B51" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="31">
         <f>C48/C50</f>
         <v>232.78928978178433</v>
       </c>
@@ -4778,7 +4776,7 @@
       <c r="B52" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C52" s="33">
+      <c r="C52" s="32">
         <f>C49/C50</f>
         <v>225.77772285257046</v>
       </c>
@@ -4787,7 +4785,7 @@
       <c r="B53" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="33">
         <f>Assumptions!$C$6</f>
         <v>169.79</v>
       </c>
@@ -4796,7 +4794,7 @@
       <c r="B54" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C54" s="35">
+      <c r="C54" s="34">
         <f>C51/C53-1</f>
         <v>0.37104240403901501</v>
       </c>
@@ -4805,7 +4803,7 @@
       <c r="B55" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C55" s="36">
+      <c r="C55" s="35">
         <f>C52/C53-1</f>
         <v>0.32974688057347601</v>
       </c>
@@ -4819,7 +4817,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:H62"/>
+  <dimension ref="B2:H63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -4839,23 +4837,23 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="18"/>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>216</v>
       </c>
     </row>
@@ -4874,647 +4872,656 @@
       <c r="B7" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>'Income Statement'!F27</f>
         <v>1945.5000000000009</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C8" s="11">
+        <f>'Income Statement'!E27</f>
+        <v>3353.2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="26">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C9" s="11">
-        <f>C7*C8</f>
-        <v>36964.500000000015</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="37">
-        <v>4.0000000000000001E-3</v>
+      <c r="C10" s="10">
+        <f>C8*C9</f>
+        <v>50298</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="36">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C11" s="22">
-        <f>C9*C10</f>
-        <v>147.85800000000006</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="6" t="s">
+      <c r="C12" s="21">
+        <f>C10*C11</f>
+        <v>201.19200000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B14" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C14" s="22">
-        <f>C9</f>
-        <v>36964.500000000015</v>
-      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C15" s="21">
+        <f>C10</f>
+        <v>50298</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C15" s="22">
-        <f>C11</f>
-        <v>147.85800000000006</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="21">
+        <f>C12</f>
+        <v>201.19200000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C16" s="11">
-        <f>C14+C15</f>
-        <v>37112.358000000015</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C18" s="26">
-        <v>4</v>
+      <c r="C17" s="10">
+        <f>C15+C16</f>
+        <v>50499.192000000003</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C19" s="22">
-        <f>C7*C18</f>
-        <v>7782.0000000000036</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="21">
+        <f>C8*C19</f>
+        <v>13412.8</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C20" s="11">
-        <f>C16-C19</f>
-        <v>29330.358000000011</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="10">
+        <f>C17-C20</f>
+        <v>37086.392000000007</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C21" s="22">
-        <f>C19+C20</f>
-        <v>37112.358000000015</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="6" t="s">
+      <c r="C22" s="21">
+        <f>C20+C21</f>
+        <v>50499.19200000001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C24" s="16">
-        <v>0.10249999999999999</v>
-      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C25" s="15">
+        <v>0.10249999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B26" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C26" s="27">
         <f>Assumptions!$C$24</f>
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B26" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C26" s="16">
-        <v>0.2175</v>
-      </c>
-    </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C27" s="16">
-        <v>4.1200000000000001E-2</v>
+        <v>234</v>
+      </c>
+      <c r="C27" s="15">
+        <v>0.2175</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C28" s="16">
-        <v>0.03</v>
+        <v>235</v>
+      </c>
+      <c r="C28" s="15">
+        <v>4.1200000000000001E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C29" s="15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B30" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C30" s="15">
         <v>0.7</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="6" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B32" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D33" s="15">
         <v>0.06</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E33" s="15">
         <v>0.06</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F33" s="15">
         <v>0.06</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G33" s="15">
         <v>0.06</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H33" s="15">
         <v>0.06</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="4" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B34" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C33" s="11">
-        <f>C7</f>
-        <v>1945.5000000000009</v>
-      </c>
-      <c r="D33" s="11">
-        <f>C33*(1+D32)</f>
-        <v>2062.2300000000009</v>
-      </c>
-      <c r="E33" s="11">
-        <f>D33*(1+E32)</f>
-        <v>2185.9638000000009</v>
-      </c>
-      <c r="F33" s="11">
-        <f>E33*(1+F32)</f>
-        <v>2317.1216280000012</v>
-      </c>
-      <c r="G33" s="11">
-        <f>F33*(1+G32)</f>
-        <v>2456.1489256800014</v>
-      </c>
-      <c r="H33" s="11">
-        <f>G33*(1+H32)</f>
-        <v>2603.5178612208015</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B35" s="6" t="s">
+      <c r="C34" s="10">
+        <f>C8</f>
+        <v>3353.2</v>
+      </c>
+      <c r="D34" s="10">
+        <f>C34*(1+D33)</f>
+        <v>3554.3919999999998</v>
+      </c>
+      <c r="E34" s="10">
+        <f>D34*(1+E33)</f>
+        <v>3767.6555199999998</v>
+      </c>
+      <c r="F34" s="10">
+        <f>E34*(1+F33)</f>
+        <v>3993.7148511999999</v>
+      </c>
+      <c r="G34" s="10">
+        <f>F34*(1+G33)</f>
+        <v>4233.3377422720005</v>
+      </c>
+      <c r="H34" s="10">
+        <f>G34*(1+H33)</f>
+        <v>4487.3380068083206</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D36" s="22">
-        <f>D33</f>
-        <v>2062.2300000000009</v>
-      </c>
-      <c r="E36" s="22">
-        <f>E33</f>
-        <v>2185.9638000000009</v>
-      </c>
-      <c r="F36" s="22">
-        <f>F33</f>
-        <v>2317.1216280000012</v>
-      </c>
-      <c r="G36" s="22">
-        <f>G33</f>
-        <v>2456.1489256800014</v>
-      </c>
-      <c r="H36" s="22">
-        <f>H33</f>
-        <v>2603.5178612208015</v>
-      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="D37" s="22">
-        <f>-D33*$C$26</f>
-        <v>-448.53502500000019</v>
-      </c>
-      <c r="E37" s="22">
-        <f>-E33*$C$26</f>
-        <v>-475.44712650000019</v>
-      </c>
-      <c r="F37" s="22">
-        <f>-F33*$C$26</f>
-        <v>-503.97395409000029</v>
-      </c>
-      <c r="G37" s="22">
-        <f>-G33*$C$26</f>
-        <v>-534.2123913354003</v>
-      </c>
-      <c r="H37" s="22">
-        <f>-H33*$C$26</f>
-        <v>-566.26513481552433</v>
+        <v>170</v>
+      </c>
+      <c r="D37" s="21">
+        <f>D34</f>
+        <v>3554.3919999999998</v>
+      </c>
+      <c r="E37" s="21">
+        <f>E34</f>
+        <v>3767.6555199999998</v>
+      </c>
+      <c r="F37" s="21">
+        <f>F34</f>
+        <v>3993.7148511999999</v>
+      </c>
+      <c r="G37" s="21">
+        <f>G34</f>
+        <v>4233.3377422720005</v>
+      </c>
+      <c r="H37" s="21">
+        <f>H34</f>
+        <v>4487.3380068083206</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D38" s="22">
-        <f>-D45*$C$24</f>
-        <v>-797.65500000000031</v>
-      </c>
-      <c r="E38" s="22">
-        <f>-E45*$C$24</f>
-        <v>-746.67642206378662</v>
-      </c>
-      <c r="F38" s="22">
-        <f>-F45*$C$24</f>
-        <v>-687.14836233689402</v>
-      </c>
-      <c r="G38" s="22">
-        <f>-G45*$C$24</f>
-        <v>-618.22889319059288</v>
-      </c>
-      <c r="H38" s="22">
-        <f>-H45*$C$24</f>
-        <v>-539.00586301023907</v>
+        <v>241</v>
+      </c>
+      <c r="D38" s="21">
+        <f>-D34*$C$27</f>
+        <v>-773.08025999999995</v>
+      </c>
+      <c r="E38" s="21">
+        <f>-E34*$C$27</f>
+        <v>-819.46507559999998</v>
+      </c>
+      <c r="F38" s="21">
+        <f>-F34*$C$27</f>
+        <v>-868.63298013600001</v>
+      </c>
+      <c r="G38" s="21">
+        <f>-G34*$C$27</f>
+        <v>-920.75095894416006</v>
+      </c>
+      <c r="H38" s="21">
+        <f>-H34*$C$27</f>
+        <v>-975.99601648080977</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D39" s="22">
-        <f>-D33*$C$27</f>
-        <v>-84.963876000000042</v>
-      </c>
-      <c r="E39" s="22">
-        <f>-E33*$C$27</f>
-        <v>-90.061708560000042</v>
-      </c>
-      <c r="F39" s="22">
-        <f>-F33*$C$27</f>
-        <v>-95.465411073600052</v>
-      </c>
-      <c r="G39" s="22">
-        <f>-G33*$C$27</f>
-        <v>-101.19333573801606</v>
-      </c>
-      <c r="H39" s="22">
-        <f>-H33*$C$27</f>
-        <v>-107.26493588229702</v>
+        <v>242</v>
+      </c>
+      <c r="D39" s="21">
+        <f>-D46*$C$25</f>
+        <v>-1374.8119999999999</v>
+      </c>
+      <c r="E39" s="21">
+        <f>-E46*$C$25</f>
+        <v>-1286.9469948415767</v>
+      </c>
+      <c r="F39" s="21">
+        <f>-F46*$C$25</f>
+        <v>-1184.3463832372508</v>
+      </c>
+      <c r="G39" s="21">
+        <f>-G46*$C$25</f>
+        <v>-1065.5590463360036</v>
+      </c>
+      <c r="H39" s="21">
+        <f>-H46*$C$25</f>
+        <v>-929.01282952759311</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D40" s="38">
-        <f>D36+D37+D38+D39</f>
-        <v>731.07609900000045</v>
-      </c>
-      <c r="E40" s="38">
-        <f>E36+E37+E38+E39</f>
-        <v>873.77854287621403</v>
-      </c>
-      <c r="F40" s="38">
-        <f>F36+F37+F38+F39</f>
-        <v>1030.5339004995069</v>
-      </c>
-      <c r="G40" s="38">
-        <f>G36+G37+G38+G39</f>
-        <v>1202.5143054159923</v>
-      </c>
-      <c r="H40" s="38">
-        <f>H36+H37+H38+H39</f>
-        <v>1390.9819275127409</v>
+        <v>243</v>
+      </c>
+      <c r="D40" s="21">
+        <f>-D34*$C$28</f>
+        <v>-146.44095039999999</v>
+      </c>
+      <c r="E40" s="21">
+        <f>-E34*$C$28</f>
+        <v>-155.22740742400001</v>
+      </c>
+      <c r="F40" s="21">
+        <f>-F34*$C$28</f>
+        <v>-164.54105186944</v>
+      </c>
+      <c r="G40" s="21">
+        <f>-G34*$C$28</f>
+        <v>-174.41351498160643</v>
+      </c>
+      <c r="H40" s="21">
+        <f>-H34*$C$28</f>
+        <v>-184.87832588050281</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D41" s="37">
+        <f>D37+D38+D39+D40</f>
+        <v>1260.0587896000002</v>
+      </c>
+      <c r="E41" s="37">
+        <f>E37+E38+E39+E40</f>
+        <v>1506.0160421344231</v>
+      </c>
+      <c r="F41" s="37">
+        <f>F37+F38+F39+F40</f>
+        <v>1776.1944359573088</v>
+      </c>
+      <c r="G41" s="37">
+        <f>G37+G38+G39+G40</f>
+        <v>2072.6142220102302</v>
+      </c>
+      <c r="H41" s="37">
+        <f>H37+H38+H39+H40</f>
+        <v>2397.4508349194148</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D41" s="22">
-        <f>-MAX(0,D40)*$C$25</f>
-        <v>-120.62755633500008</v>
-      </c>
-      <c r="E41" s="22">
-        <f>-MAX(0,E40)*$C$25</f>
-        <v>-144.17345957457533</v>
-      </c>
-      <c r="F41" s="22">
-        <f>-MAX(0,F40)*$C$25</f>
-        <v>-170.03809358241864</v>
-      </c>
-      <c r="G41" s="22">
-        <f>-MAX(0,G40)*$C$25</f>
-        <v>-198.41486039363875</v>
-      </c>
-      <c r="H41" s="22">
-        <f>-MAX(0,H40)*$C$25</f>
-        <v>-229.51201803960225</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="4" t="s">
+      <c r="D42" s="21">
+        <f>-MAX(0,D41)*$C$26</f>
+        <v>-207.90970028400005</v>
+      </c>
+      <c r="E42" s="21">
+        <f>-MAX(0,E41)*$C$26</f>
+        <v>-248.49264695217983</v>
+      </c>
+      <c r="F42" s="21">
+        <f>-MAX(0,F41)*$C$26</f>
+        <v>-293.07208193295594</v>
+      </c>
+      <c r="G42" s="21">
+        <f>-MAX(0,G41)*$C$26</f>
+        <v>-341.98134663168798</v>
+      </c>
+      <c r="H42" s="21">
+        <f>-MAX(0,H41)*$C$26</f>
+        <v>-395.57938776170346</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B43" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="D42" s="11">
-        <f>D40+D41</f>
-        <v>610.44854266500033</v>
-      </c>
-      <c r="E42" s="11">
-        <f>E40+E41</f>
-        <v>729.60508330163873</v>
-      </c>
-      <c r="F42" s="11">
-        <f>F40+F41</f>
-        <v>860.4958069170882</v>
-      </c>
-      <c r="G42" s="11">
-        <f>G40+G41</f>
-        <v>1004.0994450223536</v>
-      </c>
-      <c r="H42" s="11">
-        <f>H40+H41</f>
-        <v>1161.4699094731386</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="6" t="s">
+      <c r="D43" s="10">
+        <f>D41+D42</f>
+        <v>1052.1490893160001</v>
+      </c>
+      <c r="E43" s="10">
+        <f>E41+E42</f>
+        <v>1257.5233951822433</v>
+      </c>
+      <c r="F43" s="10">
+        <f>F41+F42</f>
+        <v>1483.1223540243527</v>
+      </c>
+      <c r="G43" s="10">
+        <f>G41+G42</f>
+        <v>1730.6328753785422</v>
+      </c>
+      <c r="H43" s="10">
+        <f>H41+H42</f>
+        <v>2001.8714471577114</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C45" s="22">
-        <f>C19</f>
-        <v>7782.0000000000036</v>
-      </c>
-      <c r="D45" s="22">
-        <f>C19</f>
-        <v>7782.0000000000036</v>
-      </c>
-      <c r="E45" s="22">
-        <f>D48</f>
-        <v>7284.6480201345039</v>
-      </c>
-      <c r="F45" s="22">
-        <f>E48</f>
-        <v>6703.8864618233565</v>
-      </c>
-      <c r="G45" s="22">
-        <f>F48</f>
-        <v>6031.5013969813945</v>
-      </c>
-      <c r="H45" s="22">
-        <f>G48</f>
-        <v>5258.5937854657468</v>
-      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D46" s="22">
-        <f>-MIN($C$19*$C$28,D45)</f>
-        <v>-233.46000000000009</v>
-      </c>
-      <c r="E46" s="22">
-        <f>-MIN($C$19*$C$28,E45)</f>
-        <v>-233.46000000000009</v>
-      </c>
-      <c r="F46" s="22">
-        <f>-MIN($C$19*$C$28,F45)</f>
-        <v>-233.46000000000009</v>
-      </c>
-      <c r="G46" s="22">
-        <f>-MIN($C$19*$C$28,G45)</f>
-        <v>-233.46000000000009</v>
-      </c>
-      <c r="H46" s="22">
-        <f>-MIN($C$19*$C$28,H45)</f>
-        <v>-233.46000000000009</v>
+        <v>248</v>
+      </c>
+      <c r="C46" s="21">
+        <f>C20</f>
+        <v>13412.8</v>
+      </c>
+      <c r="D46" s="21">
+        <f>C20</f>
+        <v>13412.8</v>
+      </c>
+      <c r="E46" s="21">
+        <f>D49</f>
+        <v>12555.580437478799</v>
+      </c>
+      <c r="F46" s="21">
+        <f>E49</f>
+        <v>11554.598860851229</v>
+      </c>
+      <c r="G46" s="21">
+        <f>F49</f>
+        <v>10395.698013034182</v>
+      </c>
+      <c r="H46" s="21">
+        <f>G49</f>
+        <v>9063.5398002692018</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D47" s="21">
+        <f>-MIN($C$20*$C$29,D46)</f>
+        <v>-402.38399999999996</v>
+      </c>
+      <c r="E47" s="21">
+        <f>-MIN($C$20*$C$29,E46)</f>
+        <v>-402.38399999999996</v>
+      </c>
+      <c r="F47" s="21">
+        <f>-MIN($C$20*$C$29,F46)</f>
+        <v>-402.38399999999996</v>
+      </c>
+      <c r="G47" s="21">
+        <f>-MIN($C$20*$C$29,G46)</f>
+        <v>-402.38399999999996</v>
+      </c>
+      <c r="H47" s="21">
+        <f>-MIN($C$20*$C$29,H46)</f>
+        <v>-402.38399999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="D47" s="22">
-        <f>-MIN(MAX(0,D42+D46)*$C$29,D45+D46)</f>
-        <v>-263.89197986550016</v>
-      </c>
-      <c r="E47" s="22">
-        <f>-MIN(MAX(0,E42+E46)*$C$29,E45+E46)</f>
-        <v>-347.30155831114701</v>
-      </c>
-      <c r="F47" s="22">
-        <f>-MIN(MAX(0,F42+F46)*$C$29,F45+F46)</f>
-        <v>-438.92506484196167</v>
-      </c>
-      <c r="G47" s="22">
-        <f>-MIN(MAX(0,G42+G46)*$C$29,G45+G46)</f>
-        <v>-539.44761151564751</v>
-      </c>
-      <c r="H47" s="22">
-        <f>-MIN(MAX(0,H42+H46)*$C$29,H45+H46)</f>
-        <v>-649.60693663119696</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="4" t="s">
+      <c r="D48" s="21">
+        <f>-MIN(MAX(0,D43+D47)*$C$30,D46+D47)</f>
+        <v>-454.83556252120002</v>
+      </c>
+      <c r="E48" s="21">
+        <f>-MIN(MAX(0,E43+E47)*$C$30,E46+E47)</f>
+        <v>-598.59757662757033</v>
+      </c>
+      <c r="F48" s="21">
+        <f>-MIN(MAX(0,F43+F47)*$C$30,F46+F47)</f>
+        <v>-756.51684781704682</v>
+      </c>
+      <c r="G48" s="21">
+        <f>-MIN(MAX(0,G43+G47)*$C$30,G46+G47)</f>
+        <v>-929.77421276497944</v>
+      </c>
+      <c r="H48" s="21">
+        <f>-MIN(MAX(0,H43+H47)*$C$30,H46+H47)</f>
+        <v>-1119.6412130103979</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D48" s="11">
-        <f>MAX(0,D45+D46+D47)</f>
-        <v>7284.6480201345039</v>
-      </c>
-      <c r="E48" s="11">
-        <f>MAX(0,E45+E46+E47)</f>
-        <v>6703.8864618233565</v>
-      </c>
-      <c r="F48" s="11">
-        <f>MAX(0,F45+F46+F47)</f>
-        <v>6031.5013969813945</v>
-      </c>
-      <c r="G48" s="11">
-        <f>MAX(0,G45+G46+G47)</f>
-        <v>5258.5937854657468</v>
-      </c>
-      <c r="H48" s="11">
-        <f>MAX(0,H45+H46+H47)</f>
-        <v>4375.52684883455</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="6" t="s">
+      <c r="D49" s="10">
+        <f>MAX(0,D46+D47+D48)</f>
+        <v>12555.580437478799</v>
+      </c>
+      <c r="E49" s="10">
+        <f>MAX(0,E46+E47+E48)</f>
+        <v>11554.598860851229</v>
+      </c>
+      <c r="F49" s="10">
+        <f>MAX(0,F46+F47+F48)</f>
+        <v>10395.698013034182</v>
+      </c>
+      <c r="G49" s="10">
+        <f>MAX(0,G46+G47+G48)</f>
+        <v>9063.5398002692018</v>
+      </c>
+      <c r="H49" s="10">
+        <f>MAX(0,H46+H47+H48)</f>
+        <v>7541.5145872588037</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="H51" s="26">
-        <v>21</v>
-      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="H52" s="25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B53" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="H52" s="22">
-        <f>H33</f>
-        <v>2603.5178612208015</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="4" t="s">
+      <c r="H53" s="21">
+        <f>H34</f>
+        <v>4487.3380068083206</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B54" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="H53" s="11">
-        <f>H52*H51</f>
-        <v>54673.875085636828</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="5" t="s">
+      <c r="H54" s="10">
+        <f>H53*H52</f>
+        <v>67310.07010212481</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B55" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="H54" s="22">
-        <f>-H48</f>
-        <v>-4375.52684883455</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="4" t="s">
+      <c r="H55" s="21">
+        <f>-H49</f>
+        <v>-7541.5145872588037</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B56" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="H55" s="11">
-        <f>H53+H54</f>
-        <v>50298.348236802281</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B57" s="6" t="s">
+      <c r="H56" s="10">
+        <f>H54+H55</f>
+        <v>59768.555514866006</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B58" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C58" s="22">
-        <f>C20</f>
-        <v>29330.358000000011</v>
-      </c>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C59" s="22">
-        <f>H55</f>
-        <v>50298.348236802281</v>
+        <v>259</v>
+      </c>
+      <c r="C59" s="21">
+        <f>C21</f>
+        <v>37086.392000000007</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C60" s="21">
+        <f>H56</f>
+        <v>59768.555514866006</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B61" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="28">
         <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B61" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C61" s="39">
-        <f>IFERROR(C59/C58,0)</f>
-        <v>1.7148903616110742</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C62" s="38">
+        <f>IFERROR(C60/C59,0)</f>
+        <v>1.6116034019935397</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B63" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C62" s="36">
-        <f>IFERROR((C59/C58)^(1/C60)-1,0)</f>
-        <v>0.11390273911455995</v>
+      <c r="C63" s="35">
+        <f>IFERROR((C60/C59)^(1/C61)-1,0)</f>
+        <v>0.10014932110961361</v>
       </c>
     </row>
   </sheetData>
